--- a/research/MEE.NZ/Reports/MEE.NZ_DCF_Model.xlsx
+++ b/research/MEE.NZ/Reports/MEE.NZ_DCF_Model.xlsx
@@ -1360,9 +1360,10 @@
       </c>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45">
-        <f> Cash, closing ($M)</f>
-        <v>0</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>= Cash, closing ($M)</t>
+        </is>
       </c>
       <c r="B45" s="5">
         <f>B40+B41</f>
